--- a/ProductCRMAPI/bin/Debug/Uploads/Inventory.xlsx
+++ b/ProductCRMAPI/bin/Debug/Uploads/Inventory.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>SN0</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Pcs</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>15</t>
@@ -523,20 +520,20 @@
       <c r="D2" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>12</v>
+      <c r="E2" s="0">
+        <v>17</v>
       </c>
       <c r="F2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="H2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="0" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -544,28 +541,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>17</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>12</v>
+      <c r="E3" s="0">
+        <v>19</v>
       </c>
       <c r="F3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="0" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -573,28 +570,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>19</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="0" t="s">
-        <v>12</v>
+      <c r="E4" s="0">
+        <v>16</v>
       </c>
       <c r="F4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="H4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="0" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -602,28 +599,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>21</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>12</v>
+      <c r="E5" s="0">
+        <v>17</v>
       </c>
       <c r="F5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="H5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>14</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +628,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="D6" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>12</v>
+      <c r="E6" s="0">
+        <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="H6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="0" t="s">
         <v>14</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
